--- a/data/EDA/법정동 기준 시군구 단위.xlsx
+++ b/data/EDA/법정동 기준 시군구 단위.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Playdata\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\SKN10-FINAL-5Team\Data\EDA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A2F6EF-06C1-4C14-8906-B4810E1DB8E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CAF40A-EBDC-44A9-A3BA-AA3D850F18A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{24CA9D51-535D-4E78-9AC6-608F6317D634}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{24CA9D51-535D-4E78-9AC6-608F6317D634}"/>
   </bookViews>
   <sheets>
     <sheet name="통합 버전_with시도" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="524">
   <si>
     <t>서울특별시</t>
   </si>
@@ -1537,6 +1537,109 @@
   </si>
   <si>
     <t>경상남도 함양군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도</t>
+  </si>
+  <si>
+    <t>경기도 수원시</t>
+  </si>
+  <si>
+    <t>경상남도 창원시</t>
+  </si>
+  <si>
+    <t>경상북도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기도 성남시</t>
+  </si>
+  <si>
+    <t>경기도 고양시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기도 안양시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기도 용인시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대전광역시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충청남도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원특별자치도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 익산시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충청북도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 전주시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원특별자치도 원주시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 군산시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기도 안산시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전라남도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 김제시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 순창군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세종특별자치시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 완주군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 남원시</t>
+  </si>
+  <si>
+    <t>전북특별자치도 정읍시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충청남도 천안시</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원특별자치도 홍천군</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전북특별자치도 고창군</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3922,6 +4025,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA93DC04-D47B-4B20-BD30-A4BDDDAE4C88}">
   <dimension ref="A1:B251"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -5940,7 +6046,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22D0AC12-720A-4385-8A63-27254C4A5832}">
-  <dimension ref="A1:G289"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -8399,7 +8505,7 @@
         <v>48330</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>228</v>
       </c>
@@ -8407,7 +8513,7 @@
         <v>48720</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>229</v>
       </c>
@@ -8415,7 +8521,7 @@
         <v>48170</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>230</v>
       </c>
@@ -8423,7 +8529,7 @@
         <v>48740</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>231</v>
       </c>
@@ -8431,100 +8537,353 @@
         <v>48125</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>232</v>
       </c>
       <c r="B277">
         <v>48127</v>
       </c>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G277" t="s">
+        <v>58</v>
+      </c>
+      <c r="H277">
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>233</v>
       </c>
       <c r="B278">
         <v>48123</v>
       </c>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G278" t="s">
+        <v>219</v>
+      </c>
+      <c r="H278">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>234</v>
       </c>
       <c r="B279">
         <v>48121</v>
       </c>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G279" t="s">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>235</v>
       </c>
       <c r="B280">
         <v>48129</v>
       </c>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G280" t="s">
+        <v>61</v>
+      </c>
+      <c r="H280">
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>236</v>
       </c>
       <c r="B281">
         <v>48220</v>
       </c>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G281" t="s">
+        <v>497</v>
+      </c>
+      <c r="H281">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>237</v>
       </c>
       <c r="B282">
         <v>48850</v>
       </c>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G282" t="s">
+        <v>241</v>
+      </c>
+      <c r="H282">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>238</v>
       </c>
       <c r="B283">
         <v>48730</v>
       </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G283" t="s">
+        <v>41</v>
+      </c>
+      <c r="H283">
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>239</v>
       </c>
       <c r="B284">
         <v>48870</v>
       </c>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G284" t="s">
+        <v>498</v>
+      </c>
+      <c r="H284">
+        <v>41110</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>240</v>
       </c>
       <c r="B285">
         <v>48890</v>
       </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G285" t="s">
+        <v>26</v>
+      </c>
+      <c r="H285">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G286" t="s">
+        <v>53</v>
+      </c>
+      <c r="H286">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>241</v>
       </c>
       <c r="B287" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G287" t="s">
+        <v>499</v>
+      </c>
+      <c r="H287">
+        <v>48120</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>494</v>
       </c>
       <c r="B288">
         <v>50130</v>
       </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="G288" t="s">
+        <v>500</v>
+      </c>
+      <c r="H288">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>495</v>
       </c>
       <c r="B289">
         <v>50110</v>
+      </c>
+      <c r="G289" t="s">
+        <v>501</v>
+      </c>
+      <c r="H289">
+        <v>41130</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G290" t="s">
+        <v>502</v>
+      </c>
+      <c r="H290">
+        <v>41280</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G291" t="s">
+        <v>503</v>
+      </c>
+      <c r="H291">
+        <v>41170</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G292" t="s">
+        <v>504</v>
+      </c>
+      <c r="H292">
+        <v>41460</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G293" t="s">
+        <v>505</v>
+      </c>
+      <c r="H293">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G294" t="s">
+        <v>506</v>
+      </c>
+      <c r="H294">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G295" t="s">
+        <v>507</v>
+      </c>
+      <c r="H295">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G296" t="s">
+        <v>508</v>
+      </c>
+      <c r="H296">
+        <v>52140</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G297" t="s">
+        <v>509</v>
+      </c>
+      <c r="H297">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G298" t="s">
+        <v>510</v>
+      </c>
+      <c r="H298">
+        <v>52110</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G299" t="s">
+        <v>511</v>
+      </c>
+      <c r="H299">
+        <v>51130</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G300" t="s">
+        <v>512</v>
+      </c>
+      <c r="H300">
+        <v>52130</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G301" t="s">
+        <v>513</v>
+      </c>
+      <c r="H301">
+        <v>41270</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G302" t="s">
+        <v>514</v>
+      </c>
+      <c r="H302">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G303" t="s">
+        <v>515</v>
+      </c>
+      <c r="H303">
+        <v>52210</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G304" t="s">
+        <v>516</v>
+      </c>
+      <c r="H304">
+        <v>52770</v>
+      </c>
+    </row>
+    <row r="305" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G305" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="306" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G306" t="s">
+        <v>518</v>
+      </c>
+      <c r="H306">
+        <v>52710</v>
+      </c>
+    </row>
+    <row r="307" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G307" t="s">
+        <v>519</v>
+      </c>
+      <c r="H307">
+        <v>52190</v>
+      </c>
+    </row>
+    <row r="308" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G308" t="s">
+        <v>520</v>
+      </c>
+      <c r="H308">
+        <v>52180</v>
+      </c>
+    </row>
+    <row r="309" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G309" t="s">
+        <v>521</v>
+      </c>
+      <c r="H309">
+        <v>44130</v>
+      </c>
+    </row>
+    <row r="310" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G310" t="s">
+        <v>522</v>
+      </c>
+      <c r="H310">
+        <v>51720</v>
+      </c>
+    </row>
+    <row r="311" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G311" t="s">
+        <v>523</v>
+      </c>
+      <c r="H311">
+        <v>52790</v>
       </c>
     </row>
   </sheetData>
